--- a/docs/review/packs/chapter-3.7.xlsx
+++ b/docs/review/packs/chapter-3.7.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>108</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -2932,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Expect a complete tear to change several examination findings, through the secondary roles.</t>
+          <t>State a direction and a flexion angle with any claim about what the ligament does.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Treat the functional loss as partly neuromuscular rather than purely mechanical.</t>
+          <t>Expect a complete tear to change several examination findings, through the secondary roles.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Treat the four functions as unequally restorable.</t>
+          <t>Treat the functional loss as partly neuromuscular rather than purely mechanical.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -3106,12 +3106,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Address the secondary restraints where they are also injured, rather than relying on the graft.</t>
+          <t>Read an apportionment figure with its sectioning order in mind.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -3121,22 +3121,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P1</t>
+          <t>3.7.1-P5</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3.7.2</t>
+          <t>3.7.1</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Expect a combined injury to distribute load differently from the sectioning studies.</t>
+          <t>Treat the four functions as unequally restorable.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -3146,12 +3146,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P2</t>
+          <t>3.7.1-P6</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3.7.2</t>
+          <t>3.7.1</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Treat the primary and secondary language as the framework for deciding what a reconstruction has to include.</t>
+          <t>Address the secondary restraints where they are also injured, rather than relying on the graft.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -3171,12 +3171,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P3</t>
+          <t>3.7.1-P7</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3.7.2</t>
+          <t>3.7.1</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Assess the secondary restraints before relying on a single graft to carry rotation.</t>
+          <t>Read a construct study by which of the four functions it measured.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -3196,7 +3196,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P4</t>
+          <t>3.7.2-P1</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where the restraint is meeting an excessive load.</t>
+          <t>Expect a combined injury to distribute load differently from the sectioning studies.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -3221,22 +3221,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P1</t>
+          <t>3.7.2-P2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3.7.3</t>
+          <t>3.7.2</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Expect a chronically deficient knee to be more lax than an acutely injured one.</t>
+          <t>Treat the primary and secondary language as the framework for deciding what a reconstruction has to include.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -3246,22 +3246,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P2</t>
+          <t>3.7.2-P3</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>3.7.3</t>
+          <t>3.7.2</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where laxity exceeds what the injury explains.</t>
+          <t>Decide whether to augment by asking which share is not being restored.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -3271,22 +3271,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P3</t>
+          <t>3.7.2-P4</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3.7.3</t>
+          <t>3.7.2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Treat examination under anaesthetic as the more complete structural assessment.</t>
+          <t>Assess the secondary restraints before relying on a single graft to carry rotation.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -3296,12 +3296,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P4</t>
+          <t>3.7.2-P5</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3.7.3</t>
+          <t>3.7.2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Treat secondary restraint injury as the commonest reason a reconstruction underperforms without a technical error.</t>
+          <t>Measure slope where the restraint is meeting an excessive load.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -3321,12 +3321,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P5</t>
+          <t>3.7.2-P6</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3.7.3</t>
+          <t>3.7.2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Measure slope before revising a graft that failed without a new injury.</t>
+          <t>Read construct comparisons with the sectioning order limitation in mind.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -3346,7 +3346,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P6</t>
+          <t>3.7.3-P1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Repair the secondary restraints at the index operation rather than later.</t>
+          <t>Expect a chronically deficient knee to be more lax than an acutely injured one.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -3371,12 +3371,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P1</t>
+          <t>3.7.3-P2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>3.7.4</t>
+          <t>3.7.3</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Treat the two bundle model as functionally useful and anatomically approximate.</t>
+          <t>Measure slope where laxity exceeds what the injury explains.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -3396,12 +3396,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P2</t>
+          <t>3.7.3-P3</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3.7.4</t>
+          <t>3.7.3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Expect a partial tear to produce angle specific findings.</t>
+          <t>Treat examination under anaesthetic as the more complete structural assessment.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -3421,22 +3421,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P3</t>
+          <t>3.7.3-P4</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>3.7.4</t>
+          <t>3.7.3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Place a femoral tunnel knowing it is the main determinant of length change behaviour.</t>
+          <t>Treat secondary restraint injury as the commonest reason a reconstruction underperforms without a technical error.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -3446,22 +3446,22 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P4</t>
+          <t>3.7.3-P5</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>3.7.4</t>
+          <t>3.7.3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Avoid quoting a single tension figure for the whole ligament.</t>
+          <t>Measure slope before revising a graft that failed without a new injury.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -3471,12 +3471,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P5</t>
+          <t>3.7.3-P6</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.7.4</t>
+          <t>3.7.3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Treat the bundle model as the mechanical content of the tunnel position debate.</t>
+          <t>Repair the secondary restraints at the index operation rather than later.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P6</t>
+          <t>3.7.4-P1</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Place the graft in the native footprint centre rather than aiming at a bundle.</t>
+          <t>Treat the two bundle model as functionally useful and anatomically approximate.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -3521,12 +3521,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P1</t>
+          <t>3.7.4-P2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.7.5</t>
+          <t>3.7.4</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Expect a partial tear with an endpoint to involve this bundle commonly.</t>
+          <t>Expect a partial tear to produce angle specific findings.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -3546,12 +3546,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P2</t>
+          <t>3.7.4-P3</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.7.5</t>
+          <t>3.7.4</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Place a single graft knowing it approximates this bundle's behaviour most closely.</t>
+          <t>Place a femoral tunnel knowing it is the main determinant of length change behaviour.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -3571,22 +3571,22 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P3</t>
+          <t>3.7.4-P4</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.7.5</t>
+          <t>3.7.4</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Treat the anteromedial bundle as the behaviour a single bundle reconstruction most nearly reproduces, and treat that as a partial restoration rather than a success.</t>
+          <t>Avoid quoting a single tension figure for the whole ligament.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -3596,12 +3596,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P4</t>
+          <t>3.7.4-P5</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.7.5</t>
+          <t>3.7.4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Expect a more anteromedial tunnel to restore translation and leave rotation.</t>
+          <t>Treat the bundle model as the mechanical content of the tunnel position debate.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -3621,12 +3621,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P5</t>
+          <t>3.7.4-P6</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.7.5</t>
+          <t>3.7.4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Treat a normal arthrometer reading as evidence about this bundle only.</t>
+          <t>Place the graft in the native footprint centre rather than aiming at a bundle.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -3646,22 +3646,22 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P1</t>
+          <t>3.7.4-P7</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.7.6</t>
+          <t>3.7.4</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation near extension, since that is where this bundle's share is highest.</t>
+          <t>State the gap between cadaveric and clinical evidence when the double bundle question arises.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -3671,12 +3671,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P2</t>
+          <t>3.7.5-P1</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.7.6</t>
+          <t>3.7.5</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Expect a near normal drawer at 90 degrees in a knee with a positive pivot shift.</t>
+          <t>Read a test at 90 degrees as sampling this bundle rather than the whole ligament.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -3696,12 +3696,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P3</t>
+          <t>3.7.5-P2</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.7.6</t>
+          <t>3.7.5</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Treat isolated injury to this bundle as uncommon and the sectioning evidence as the main source.</t>
+          <t>Expect a partial tear with an endpoint to involve this bundle commonly.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -3721,22 +3721,22 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P4</t>
+          <t>3.7.5-P3</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.7.6</t>
+          <t>3.7.5</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Treat this bundle's behaviour as the half a reconstruction most often fails to restore, and treat residual rotational laxity as the expected sign of it.</t>
+          <t>Place a single graft knowing it approximates this bundle's behaviour most closely.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -3746,12 +3746,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P5</t>
+          <t>3.7.5-P4</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.7.6</t>
+          <t>3.7.5</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Place the femoral tunnel to reproduce near extension rotational control.</t>
+          <t>Treat the anteromedial bundle as the behaviour a single bundle reconstruction most nearly reproduces, and treat that as a partial restoration rather than a success.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -3771,12 +3771,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P6</t>
+          <t>3.7.5-P5</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.7.6</t>
+          <t>3.7.5</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation where rotational laxity is high or the knee is a revision.</t>
+          <t>Expect a more anteromedial tunnel to restore translation and leave rotation.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -3796,12 +3796,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P7</t>
+          <t>3.7.5-P6</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.7.6</t>
+          <t>3.7.5</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Measure slope, which raises the demand on this control.</t>
+          <t>Treat a normal arthrometer reading as evidence about this bundle only.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -3821,7 +3821,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P8</t>
+          <t>3.7.6-P1</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Expect residual rotational laxity to be the sign that this behaviour was not restored.</t>
+          <t>Assess rotation near extension, since that is where this bundle's share is highest.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -3846,12 +3846,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P1</t>
+          <t>3.7.6-P2</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.7.7</t>
+          <t>3.7.6</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation near extension and record the grade, accepting its modest reliability.</t>
+          <t>Expect a near normal drawer at 90 degrees in a knee with a positive pivot shift.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -3871,12 +3871,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P2</t>
+          <t>3.7.6-P3</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.7.7</t>
+          <t>3.7.6</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Measure slope and plateau morphology where rotatory laxity is prominent.</t>
+          <t>Compare bundles by strain rather than by force, given their different dimensions.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -3896,12 +3896,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P3</t>
+          <t>3.7.6-P4</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.7.7</t>
+          <t>3.7.6</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Treat rotatory laxity as a combined motion rather than a single measurement.</t>
+          <t>Treat isolated injury to this bundle as uncommon and the sectioning evidence as the main source.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -3921,12 +3921,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P4</t>
+          <t>3.7.6-P5</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.7.7</t>
+          <t>3.7.6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Treat rotational control as the outcome that decides whether a pivoting athlete is satisfied, and as the one the evidence base measures least well.</t>
+          <t>Treat this bundle's behaviour as the half a reconstruction most often fails to restore, and treat residual rotational laxity as the expected sign of it.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -3946,12 +3946,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P5</t>
+          <t>3.7.6-P6</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.7.7</t>
+          <t>3.7.6</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation by rotational demand and laxity grade rather than by translation.</t>
+          <t>Place the femoral tunnel to reproduce near extension rotational control.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -3971,12 +3971,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P6</t>
+          <t>3.7.6-P7</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.7.7</t>
+          <t>3.7.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Repair the lateral posterior horn where it is torn, on rotational grounds.</t>
+          <t>Consider lateral augmentation where rotational laxity is high or the knee is a revision.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -3996,12 +3996,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P7</t>
+          <t>3.7.6-P8</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.7.7</t>
+          <t>3.7.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in a pivoting athlete, particularly before revision.</t>
+          <t>Measure slope, which raises the demand on this control.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -4021,22 +4021,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P1</t>
+          <t>3.7.6-P9</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.7.8</t>
+          <t>3.7.6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Applied load and flexion angle, both of which must be stated.</t>
+          <t>Expect residual rotational laxity to be the sign that this behaviour was not restored.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -4046,12 +4046,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P2</t>
+          <t>3.7.7-P1</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.7.8</t>
+          <t>3.7.7</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Treat the 3 millimetre threshold as a convention rather than a boundary.</t>
+          <t>Assess rotation near extension and record the grade, accepting its modest reliability.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -4071,12 +4071,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P3</t>
+          <t>3.7.7-P2</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.7.8</t>
+          <t>3.7.7</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Recognise that translation dominates the literature because it is measurable, not because it matters most.</t>
+          <t>Measure slope and plateau morphology where rotatory laxity is prominent.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -4096,22 +4096,22 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P4</t>
+          <t>3.7.7-P3</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.7.8</t>
+          <t>3.7.7</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Treat restored anterior translation as a necessary and insufficient result.</t>
+          <t>Treat rotatory laxity as a combined motion rather than a single measurement.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -4121,12 +4121,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P5</t>
+          <t>3.7.7-P4</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.7.8</t>
+          <t>3.7.7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Treat restored translation as the threshold rather than the goal.</t>
+          <t>Treat rotational control as the outcome that decides whether a pivoting athlete is satisfied, and as the one the evidence base measures least well.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -4146,12 +4146,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P6</t>
+          <t>3.7.7-P5</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.7.8</t>
+          <t>3.7.7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Measure serially where progressive laxity is suspected, rather than once.</t>
+          <t>Consider lateral augmentation by rotational demand and laxity grade rather than by translation.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -4171,22 +4171,22 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P1</t>
+          <t>3.7.7-P6</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.7.9</t>
+          <t>3.7.7</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Treat instrumented measures as research tools without a clinical threshold.</t>
+          <t>Repair the lateral posterior horn where it is torn, on rotational grounds.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -4196,12 +4196,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P2</t>
+          <t>3.7.7-P7</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.7.9</t>
+          <t>3.7.7</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Treat the pivot shift as the clinical sign that corresponds to what the patient reports, and treat its measurement as the weakest link in the whole chapter.</t>
+          <t>Measure slope in a pivoting athlete, particularly before revision.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -4221,22 +4221,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P3</t>
+          <t>3.7.8-P1</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.7.9</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Check the pivot shift under anaesthetic after fixation, before leaving theatre.</t>
+          <t>Applied load and flexion angle, both of which must be stated.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -4246,22 +4246,22 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P4</t>
+          <t>3.7.8-P2</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.7.9</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Address slope and lateral meniscal pathology as part of abolishing the sign.</t>
+          <t>State load, angle and the instrument's limit of agreement with any figure.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -4271,22 +4271,22 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.7.10-P1</t>
+          <t>3.7.8-P3</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.7.10</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Treat the strain data as the mechanical basis of rehabilitation protocols, and treat the protocols as having outrun the data.</t>
+          <t>Treat the 3 millimetre threshold as a convention rather than a boundary.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -4296,22 +4296,22 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.7.10-P2</t>
+          <t>3.7.8-P4</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.7.10</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Protect the graft in the first months by angle and by loading mode.</t>
+          <t>Read the curve shape and the endpoint rather than the number alone.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -4321,22 +4321,22 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.7.10-P3</t>
+          <t>3.7.8-P5</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.7.10</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Follow outcome based protocols rather than strain based ones where they differ.</t>
+          <t>Recognise that translation dominates the literature because it is measurable, not because it matters most.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -4346,22 +4346,22 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P1</t>
+          <t>3.7.8-P6</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>3.7.11</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Expect downhill running to load the ligament more than level running.</t>
+          <t>Treat restored anterior translation as a necessary and insufficient result.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -4371,22 +4371,22 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P2</t>
+          <t>3.7.8-P7</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>3.7.11</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Treat fatigue as a loading variable rather than only a performance one.</t>
+          <t>Treat restored translation as the threshold rather than the goal.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -4396,12 +4396,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P3</t>
+          <t>3.7.8-P8</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>3.7.11</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Treat running as the benchmark the other activities are read against, and as the milestone whose safety is mechanically defensible rather than conventional.</t>
+          <t>Measure serially where progressive laxity is suspected, rather than once.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -4421,22 +4421,22 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P4</t>
+          <t>3.7.9-P1</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>3.7.11</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Treat gradient and surface as part of the prescription.</t>
+          <t>Grade under anaesthetic where the grade will change the operation.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -4446,12 +4446,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P1</t>
+          <t>3.7.9-P2</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>3.7.12</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Address hip and trunk control, which set the position the knee lands in.</t>
+          <t>Read a high grade as suggesting injury beyond the cruciate alone.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -4471,22 +4471,22 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P2</t>
+          <t>3.7.9-P3</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>3.7.12</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Treat landing mechanics as modifiable risk with modest predictive value for an individual, which is the honest position the prevention literature supports.</t>
+          <t>Treat instrumented measures as research tools without a clinical threshold.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -4496,12 +4496,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P3</t>
+          <t>3.7.9-P4</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>3.7.12</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Expect landing asymmetry to persist after reconstruction with normal laxity.</t>
+          <t>Treat the pivot shift as the clinical sign that corresponds to what the patient reports, and treat its measurement as the weakest link in the whole chapter.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -4521,12 +4521,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P4</t>
+          <t>3.7.9-P5</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>3.7.12</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where loading risk seems disproportionate to the injury.</t>
+          <t>Check the pivot shift under anaesthetic after fixation, before leaving theatre.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -4546,12 +4546,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P5</t>
+          <t>3.7.9-P6</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>3.7.12</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Keep population risk reduction and individual prediction apart when counselling.</t>
+          <t>Add a lateral procedure where a residual shift is anticipated or demonstrated.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -4571,22 +4571,22 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P1</t>
+          <t>3.7.9-P7</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>3.7.13</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Expect combined loading to reduce the failure load in each direction.</t>
+          <t>Address slope and lateral meniscal pathology as part of abolishing the sign.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -4596,12 +4596,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P2</t>
+          <t>3.7.9-P8</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>3.7.13</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Treat cutting as the activity that defines the reconstruction's job.</t>
+          <t>State the sign's reliability limits when it is used to compare treatments.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -4621,22 +4621,22 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P3</t>
+          <t>3.7.10-P1</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>3.7.13</t>
+          <t>3.7.10</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation in a pivoting athlete, on this activity's mechanics.</t>
+          <t>Stage rehabilitation by flexion angle, since strain is angle dependent.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -4646,12 +4646,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P4</t>
+          <t>3.7.10-P2</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>3.7.13</t>
+          <t>3.7.10</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Measure slope before revising a graft that failed without a new injury.</t>
+          <t>Treat the strain data as the mechanical basis of rehabilitation protocols, and treat the protocols as having outrun the data.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -4671,12 +4671,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P5</t>
+          <t>3.7.10-P3</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>3.7.13</t>
+          <t>3.7.10</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Repair the lateral posterior horn where torn.</t>
+          <t>Protect the graft in the first months by angle and by loading mode.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -4696,22 +4696,22 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P1</t>
+          <t>3.7.10-P4</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>3.7.14</t>
+          <t>3.7.10</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Expect the associated injuries the mechanism predicts and look for them.</t>
+          <t>Follow outcome based protocols rather than strain based ones where they differ.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -4721,22 +4721,22 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P2</t>
+          <t>3.7.10-P5</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>3.7.14</t>
+          <t>3.7.10</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Treat screening as measuring risk factors rather than establishing mechanism.</t>
+          <t>State that graft strain in a patient is not measured when discussing protocol choices.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
@@ -4746,22 +4746,22 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P3</t>
+          <t>3.7.11-P1</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>3.7.14</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Treat the mechanism as settled in outline and unsettled in detail.</t>
+          <t>Compare activities by peak strain and by direction rather than by force.</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -4771,22 +4771,22 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P4</t>
+          <t>3.7.11-P2</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>3.7.14</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in a young pivoting athlete, particularly before revision.</t>
+          <t>Expect downhill running to load the ligament more than level running.</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
@@ -4796,22 +4796,22 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P5</t>
+          <t>3.7.11-P3</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>3.7.14</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Treat previous injury as the strongest risk factor when counselling.</t>
+          <t>Treat fatigue as a loading variable rather than only a performance one.</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -4821,12 +4821,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>3.7.15-P1</t>
+          <t>3.7.11-P4</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>3.7.15</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Treat the hormonal evidence as inconsistent rather than established.</t>
+          <t>Read running loading estimates as modelled rather than measured.</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
@@ -4846,22 +4846,22 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>3.7.15-P2</t>
+          <t>3.7.11-P5</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>3.7.15</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Treat the rate difference as established and the mechanism as partly explained, and treat that as the basis for prevention rather than for prognosis.</t>
+          <t>Compare activities by peak strain, not peak force.</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
@@ -4871,12 +4871,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>3.7.15-P3</t>
+          <t>3.7.11-P6</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>3.7.15</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation in a young female pivoting athlete, on registry reinjury data.</t>
+          <t>Treat running as the benchmark the other activities are read against, and as the milestone whose safety is mechanically defensible rather than conventional.</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr"/>
@@ -4896,12 +4896,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>3.7.15-P4</t>
+          <t>3.7.11-P7</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>3.7.15</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where a graft failed without a new injury.</t>
+          <t>Stage return to running by criteria rather than by interval.</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
@@ -4921,22 +4921,22 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P1</t>
+          <t>3.7.11-P8</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>3.7.16</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Expect fixation to be the limiting factor early and the graft later.</t>
+          <t>Delay for a concurrent meniscal repair on its own grounds rather than the graft's.</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
@@ -4946,12 +4946,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P2</t>
+          <t>3.7.11-P9</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>3.7.16</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Treat graft choice as a trade rather than a ranking.</t>
+          <t>Treat gradient and surface as part of the prescription.</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -4971,12 +4971,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P3</t>
+          <t>3.7.11-P10</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>3.7.16</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Avoid allograft in young active patients, on registry failure data.</t>
+          <t>State that graft load during running is not measured in patients.</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr"/>
@@ -4996,22 +4996,22 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P4</t>
+          <t>3.7.12-P1</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>3.7.16</t>
+          <t>3.7.12</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Plan revision graft choice from tunnel condition and available autograft rather than from the primary algorithm.</t>
+          <t>Address hip and trunk control, which set the position the knee lands in.</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -5021,12 +5021,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P1</t>
+          <t>3.7.12-P2</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.12</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Place fixation close to the joint line where the technique allows, to reduce graft motion.</t>
+          <t>Read landing ligament loading as modelled rather than measured.</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
@@ -5046,22 +5046,22 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P2</t>
+          <t>3.7.12-P3</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.12</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Expect a deep flexion strength deficit after harvest and rehabilitate it.</t>
+          <t>Treat landing mechanics as modifiable risk with modest predictive value for an individual, which is the honest position the prevention literature supports.</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
@@ -5071,22 +5071,22 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P3</t>
+          <t>3.7.12-P4</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.12</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Expect slower healing at the interface than with a bone to bone graft.</t>
+          <t>Expect landing asymmetry to persist after reconstruction with normal laxity.</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr"/>
@@ -5096,12 +5096,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P4</t>
+          <t>3.7.12-P5</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.12</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Treat diameter as the variable that matters most and the one the donor tendon may not allow.</t>
+          <t>Measure slope where loading risk seems disproportionate to the injury.</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
@@ -5121,12 +5121,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P5</t>
+          <t>3.7.12-P6</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.12</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Assess tendon size before surgery rather than discovering it during.</t>
+          <t>Keep population risk reduction and individual prediction apart when counselling.</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr"/>
@@ -5146,22 +5146,22 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P6</t>
+          <t>3.7.13-P1</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.13</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Treat a regenerated tendon as unreliable graft material.</t>
+          <t>Expect combined loading to reduce the failure load in each direction.</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
@@ -5171,22 +5171,22 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P7</t>
+          <t>3.7.13-P2</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.13</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Measure tunnel width before planning a single stage revision.</t>
+          <t>Treat cutting as the activity that defines the reconstruction's job.</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
@@ -5196,22 +5196,22 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P8</t>
+          <t>3.7.13-P3</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.13</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation to share load where diameter is inadequate.</t>
+          <t>Consider lateral augmentation in a pivoting athlete, on this activity's mechanics.</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr"/>
@@ -5221,22 +5221,22 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P9</t>
+          <t>3.7.13-P4</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.13</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Plan the graft source before theatre in any revision.</t>
+          <t>Measure slope before revising a graft that failed without a new injury.</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr"/>
@@ -5246,22 +5246,22 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P1</t>
+          <t>3.7.13-P5</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.13</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Expect marginally lower measured laxity and a small effect size.</t>
+          <t>Repair the lateral posterior horn where torn.</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr"/>
@@ -5271,22 +5271,22 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P2</t>
+          <t>3.7.13-P6</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.13</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Measure patellar height after harvest where extensor symptoms persist.</t>
+          <t>State that no assessment reproduces an unanticipated cut when discussing return to sport.</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr"/>
@@ -5296,12 +5296,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P3</t>
+          <t>3.7.14-P1</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Expect less tunnel widening, which matters if revision is later needed.</t>
+          <t>Expect the associated injuries the mechanism predicts and look for them.</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr"/>
@@ -5321,22 +5321,22 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P4</t>
+          <t>3.7.14-P2</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Treat this graft as the choice where failure rate matters more than donor site, and the hamstring graft as the reverse.</t>
+          <t>Read bone bruise patterns as evidence about the position at injury.</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr"/>
@@ -5346,22 +5346,22 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P5</t>
+          <t>3.7.14-P3</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Consider it where revision is foreseeable, for tunnel preservation.</t>
+          <t>Treat screening as measuring risk factors rather than establishing mechanism.</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr"/>
@@ -5371,12 +5371,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P6</t>
+          <t>3.7.14-P4</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Assess occupation and kneeling demand before choosing.</t>
+          <t>Treat the mechanism as settled in outline and unsettled in detail.</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr"/>
@@ -5396,22 +5396,22 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P7</t>
+          <t>3.7.14-P5</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Consider bone plugs where a tunnel defect will not hold a soft tissue graft.</t>
+          <t>Measure slope in a young pivoting athlete, particularly before revision.</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
@@ -5421,22 +5421,22 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P1</t>
+          <t>3.7.14-P6</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Expect tendon to bone healing at the soft tissue end.</t>
+          <t>Treat previous injury as the strongest risk factor when counselling.</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr"/>
@@ -5446,12 +5446,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P2</t>
+          <t>3.7.14-P7</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Treat this graft as the answer to a diameter problem and as the graft whose long term evidence is still accumulating.</t>
+          <t>State that no measurement predicts an individual injury.</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
@@ -5471,22 +5471,22 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P3</t>
+          <t>3.7.15-P1</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.15</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Use it where diameter cannot be achieved from the hamstrings.</t>
+          <t>Treat the hormonal evidence as inconsistent rather than established.</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr"/>
@@ -5496,12 +5496,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P4</t>
+          <t>3.7.15-P2</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.15</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Expect harvest quality to depend on familiarity more than for a simpler harvest.</t>
+          <t>Treat the rate difference as established and the mechanism as partly explained, and treat that as the basis for prevention rather than for prognosis.</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr"/>
@@ -5521,22 +5521,22 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P5</t>
+          <t>3.7.15-P3</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.15</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Measure tendon thickness on imaging before planning the harvest.</t>
+          <t>Consider lateral augmentation in a young female pivoting athlete, on registry reinjury data.</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr"/>
@@ -5546,22 +5546,22 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P6</t>
+          <t>3.7.15-P4</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.15</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Consider it first in revision where other donor sites are used.</t>
+          <t>Measure slope where a graft failed without a new injury.</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr"/>
@@ -5571,22 +5571,22 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P7</t>
+          <t>3.7.16-P1</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Expect small numbers in the revision evidence for this graft.</t>
+          <t>Expect fixation to be the limiting factor early and the graft later.</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
@@ -5596,12 +5596,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P1</t>
+          <t>3.7.16-P2</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Place tunnels anatomically, since position dominates every other variable.</t>
+          <t>Read time zero testing as describing the day of surgery only.</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr"/>
@@ -5621,22 +5621,22 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P2</t>
+          <t>3.7.16-P3</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Expect measured laxity to change over the first year without a new injury.</t>
+          <t>Treat graft choice as a trade rather than a ranking.</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr"/>
@@ -5646,12 +5646,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P3</t>
+          <t>3.7.16-P4</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Treat the reconstruction as a construct in an environment rather than as an operation.</t>
+          <t>Avoid allograft in young active patients, on registry failure data.</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr"/>
@@ -5671,12 +5671,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P4</t>
+          <t>3.7.16-P5</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in every revision, since it is the commonest unaddressed factor.</t>
+          <t>Read time zero comparisons as a small part of the clinical choice.</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr"/>
@@ -5696,12 +5696,12 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P5</t>
+          <t>3.7.16-P6</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -5711,16 +5711,866 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Plan single or two stage revision from tunnel imaging rather than from preference.</t>
+          <t>Plan revision graft choice from tunnel condition and available autograft rather than from the primary algorithm.</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr"/>
       <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>3.7.16-P7</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>3.7.16</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Stage with bone grafting where tunnels are wide or confluent.</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>3.7.16-P8</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>3.7.16</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Accept allograft more readily in revision and in multiligament reconstruction.</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
+      <c r="G112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>3.7.16-P9</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>3.7.16</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>State that fixation choice in compromised bone rests on principle rather than data.</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17-P1</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Place fixation close to the joint line where the technique allows, to reduce graft motion.</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17-P2</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Expect a deep flexion strength deficit after harvest and rehabilitate it.</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17-P3</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Expect slower healing at the interface than with a bone to bone graft.</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
+      <c r="G116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17-P4</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Treat diameter as the variable that matters most and the one the donor tendon may not allow.</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17-P5</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Assess tendon size before surgery rather than discovering it during.</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
+      <c r="G118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17-P6</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Treat a regenerated tendon as unreliable graft material.</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
+      <c r="G119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17-P7</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Measure tunnel width before planning a single stage revision.</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
+      <c r="G120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17-P8</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Consider lateral augmentation to share load where diameter is inadequate.</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
+      <c r="G121" s="4" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17-P9</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>3.7.17</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Plan the graft source before theatre in any revision.</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
+      <c r="G122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18-P1</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Expect marginally lower measured laxity and a small effect size.</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
+      <c r="G123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18-P2</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Measure patellar height after harvest where extensor symptoms persist.</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18-P3</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Expect less tunnel widening, which matters if revision is later needed.</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
+      <c r="G125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18-P4</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Treat this graft as the choice where failure rate matters more than donor site, and the hamstring graft as the reverse.</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
+      <c r="G126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18-P5</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Consider it where revision is foreseeable, for tunnel preservation.</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
+      <c r="G127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18-P6</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Assess occupation and kneeling demand before choosing.</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
+      <c r="G128" s="4" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18-P7</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>3.7.18</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Consider bone plugs where a tunnel defect will not hold a soft tissue graft.</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
+      <c r="G129" s="4" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19-P1</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Expect tendon to bone healing at the soft tissue end.</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
+      <c r="G130" s="4" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19-P2</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Read the clinical evidence as shorter and smaller than for the other autografts.</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
+      <c r="G131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19-P3</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Treat this graft as the answer to a diameter problem and as the graft whose long term evidence is still accumulating.</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
+      <c r="G132" s="4" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19-P4</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Use it where diameter cannot be achieved from the hamstrings.</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
+      <c r="G133" s="4" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19-P5</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Expect harvest quality to depend on familiarity more than for a simpler harvest.</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
+      <c r="G134" s="4" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19-P6</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Measure tendon thickness on imaging before planning the harvest.</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
+      <c r="G135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19-P7</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Consider it first in revision where other donor sites are used.</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
+      <c r="G136" s="4" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19-P8</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Expect small numbers in the revision evidence for this graft.</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
+      <c r="G137" s="4" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P1</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Place tunnels anatomically, since position dominates every other variable.</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
+      <c r="G138" s="4" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P2</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Expect measured laxity to change over the first year without a new injury.</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
+      <c r="G139" s="4" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P3</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Treat the reconstruction as a construct in an environment rather than as an operation.</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
+      <c r="G140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P4</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Measure slope in every revision, since it is the commonest unaddressed factor.</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
+      <c r="G141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P5</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Correct the environment as part of the revision rather than afterwards.</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
+      <c r="G142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P6</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Plan single or two stage revision from tunnel imaging rather than from preference.</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
+      <c r="G143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P7</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Correct slope in a knee that has failed a conventional revision.</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
+      <c r="G144" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6407,7 +7257,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>108</f>
+        <f>142</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -6422,7 +7272,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E110,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E144,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -6452,7 +7302,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E110,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E144,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -6464,7 +7314,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E110,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E144,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -6476,7 +7326,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E110,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E144,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -6488,7 +7338,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E110,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E144,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.7.xlsx
+++ b/docs/review/packs/chapter-3.7.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
@@ -2932,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Address the secondary restraints where they are also injured, rather than relying on the graft.</t>
+          <t>Counsel that stability and normality are different outcomes, and name which the operation restores.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Read a construct study by which of the four functions it measured.</t>
+          <t>Address the secondary restraints where they are also injured, rather than relying on the graft.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -3196,22 +3196,22 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P1</t>
+          <t>3.7.1-P8</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3.7.2</t>
+          <t>3.7.1</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Expect a combined injury to distribute load differently from the sectioning studies.</t>
+          <t>Read a construct study by which of the four functions it measured.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P2</t>
+          <t>3.7.2-P1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Treat the primary and secondary language as the framework for deciding what a reconstruction has to include.</t>
+          <t>Expect a combined injury to distribute load differently from the sectioning studies.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -3246,7 +3246,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P3</t>
+          <t>3.7.2-P2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Decide whether to augment by asking which share is not being restored.</t>
+          <t>Treat the primary and secondary language as the framework for deciding what a reconstruction has to include.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P4</t>
+          <t>3.7.2-P3</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Assess the secondary restraints before relying on a single graft to carry rotation.</t>
+          <t>Decide whether to augment by asking which share is not being restored.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -3296,7 +3296,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P5</t>
+          <t>3.7.2-P4</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where the restraint is meeting an excessive load.</t>
+          <t>Assess the secondary restraints before relying on a single graft to carry rotation.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -3321,7 +3321,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.7.2-P6</t>
+          <t>3.7.2-P5</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Read construct comparisons with the sectioning order limitation in mind.</t>
+          <t>Measure slope where the restraint is meeting an excessive load.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -3346,22 +3346,22 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P1</t>
+          <t>3.7.2-P6</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>3.7.3</t>
+          <t>3.7.2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Expect a chronically deficient knee to be more lax than an acutely injured one.</t>
+          <t>Read construct comparisons with the sectioning order limitation in mind.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P2</t>
+          <t>3.7.3-P1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where laxity exceeds what the injury explains.</t>
+          <t>Expect a chronically deficient knee to be more lax than an acutely injured one.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -3396,7 +3396,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P3</t>
+          <t>3.7.3-P2</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Treat examination under anaesthetic as the more complete structural assessment.</t>
+          <t>Measure slope where laxity exceeds what the injury explains.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P4</t>
+          <t>3.7.3-P3</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Treat secondary restraint injury as the commonest reason a reconstruction underperforms without a technical error.</t>
+          <t>Treat examination under anaesthetic as the more complete structural assessment.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -3446,7 +3446,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P5</t>
+          <t>3.7.3-P4</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Measure slope before revising a graft that failed without a new injury.</t>
+          <t>Treat secondary restraint injury as the commonest reason a reconstruction underperforms without a technical error.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -3471,7 +3471,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.7.3-P6</t>
+          <t>3.7.3-P5</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Repair the secondary restraints at the index operation rather than later.</t>
+          <t>Measure slope before revising a graft that failed without a new injury.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -3496,22 +3496,22 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P1</t>
+          <t>3.7.3-P6</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3.7.4</t>
+          <t>3.7.3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Treat the two bundle model as functionally useful and anatomically approximate.</t>
+          <t>Repair the secondary restraints at the index operation rather than later.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -3521,7 +3521,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P2</t>
+          <t>3.7.4-P1</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Expect a partial tear to produce angle specific findings.</t>
+          <t>Treat the two bundle model as functionally useful and anatomically approximate.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -3546,7 +3546,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P3</t>
+          <t>3.7.4-P2</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Place a femoral tunnel knowing it is the main determinant of length change behaviour.</t>
+          <t>Expect a partial tear to produce angle specific findings.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -3571,7 +3571,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P4</t>
+          <t>3.7.4-P3</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Avoid quoting a single tension figure for the whole ligament.</t>
+          <t>Place a femoral tunnel knowing it is the main determinant of length change behaviour.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -3596,7 +3596,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P5</t>
+          <t>3.7.4-P4</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Treat the bundle model as the mechanical content of the tunnel position debate.</t>
+          <t>Avoid quoting a single tension figure for the whole ligament.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P6</t>
+          <t>3.7.4-P5</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Place the graft in the native footprint centre rather than aiming at a bundle.</t>
+          <t>Treat the bundle model as the mechanical content of the tunnel position debate.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.7.4-P7</t>
+          <t>3.7.4-P6</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>State the gap between cadaveric and clinical evidence when the double bundle question arises.</t>
+          <t>Place the graft in the native footprint centre rather than aiming at a bundle.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -3671,22 +3671,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P1</t>
+          <t>3.7.4-P7</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.7.5</t>
+          <t>3.7.4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Read a test at 90 degrees as sampling this bundle rather than the whole ligament.</t>
+          <t>State the gap between cadaveric and clinical evidence when the double bundle question arises.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -3696,7 +3696,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P2</t>
+          <t>3.7.5-P1</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Expect a partial tear with an endpoint to involve this bundle commonly.</t>
+          <t>Read a test at 90 degrees as sampling this bundle rather than the whole ligament.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -3721,7 +3721,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P3</t>
+          <t>3.7.5-P2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Place a single graft knowing it approximates this bundle's behaviour most closely.</t>
+          <t>Expect a partial tear with an endpoint to involve this bundle commonly.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P4</t>
+          <t>3.7.5-P3</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Treat the anteromedial bundle as the behaviour a single bundle reconstruction most nearly reproduces, and treat that as a partial restoration rather than a success.</t>
+          <t>Place a single graft knowing it approximates this bundle's behaviour most closely.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -3771,7 +3771,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P5</t>
+          <t>3.7.5-P4</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Expect a more anteromedial tunnel to restore translation and leave rotation.</t>
+          <t>Treat the anteromedial bundle as the behaviour a single bundle reconstruction most nearly reproduces, and treat that as a partial restoration rather than a success.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -3796,7 +3796,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.7.5-P6</t>
+          <t>3.7.5-P5</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Treat a normal arthrometer reading as evidence about this bundle only.</t>
+          <t>Expect a more anteromedial tunnel to restore translation and leave rotation.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -3821,22 +3821,22 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P1</t>
+          <t>3.7.5-P6</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.7.6</t>
+          <t>3.7.5</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation near extension, since that is where this bundle's share is highest.</t>
+          <t>Treat a normal arthrometer reading as evidence about this bundle only.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -3846,7 +3846,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P2</t>
+          <t>3.7.6-P1</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Expect a near normal drawer at 90 degrees in a knee with a positive pivot shift.</t>
+          <t>Assess rotation near extension, since that is where this bundle's share is highest.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -3871,7 +3871,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P3</t>
+          <t>3.7.6-P2</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Compare bundles by strain rather than by force, given their different dimensions.</t>
+          <t>Expect a near normal drawer at 90 degrees in a knee with a positive pivot shift.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P4</t>
+          <t>3.7.6-P3</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Treat isolated injury to this bundle as uncommon and the sectioning evidence as the main source.</t>
+          <t>Compare bundles by strain rather than by force, given their different dimensions.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -3921,7 +3921,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P5</t>
+          <t>3.7.6-P4</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Treat this bundle's behaviour as the half a reconstruction most often fails to restore, and treat residual rotational laxity as the expected sign of it.</t>
+          <t>Treat isolated injury to this bundle as uncommon and the sectioning evidence as the main source.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -3946,7 +3946,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P6</t>
+          <t>3.7.6-P5</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Place the femoral tunnel to reproduce near extension rotational control.</t>
+          <t>Treat this bundle's behaviour as the half a reconstruction most often fails to restore, and treat residual rotational laxity as the expected sign of it.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P7</t>
+          <t>3.7.6-P6</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation where rotational laxity is high or the knee is a revision.</t>
+          <t>Place the femoral tunnel to reproduce near extension rotational control.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P8</t>
+          <t>3.7.6-P7</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Measure slope, which raises the demand on this control.</t>
+          <t>Consider lateral augmentation where rotational laxity is high or the knee is a revision.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -4021,7 +4021,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.7.6-P9</t>
+          <t>3.7.6-P8</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Expect residual rotational laxity to be the sign that this behaviour was not restored.</t>
+          <t>Measure slope, which raises the demand on this control.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -4046,22 +4046,22 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P1</t>
+          <t>3.7.6-P9</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.7.7</t>
+          <t>3.7.6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation near extension and record the grade, accepting its modest reliability.</t>
+          <t>Expect residual rotational laxity to be the sign that this behaviour was not restored.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -4071,7 +4071,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P2</t>
+          <t>3.7.7-P1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Measure slope and plateau morphology where rotatory laxity is prominent.</t>
+          <t>Assess rotation near extension and record the grade, accepting its modest reliability.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -4096,7 +4096,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P3</t>
+          <t>3.7.7-P2</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Treat rotatory laxity as a combined motion rather than a single measurement.</t>
+          <t>Measure slope and plateau morphology where rotatory laxity is prominent.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -4121,7 +4121,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P4</t>
+          <t>3.7.7-P3</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Treat rotational control as the outcome that decides whether a pivoting athlete is satisfied, and as the one the evidence base measures least well.</t>
+          <t>Treat rotatory laxity as a combined motion rather than a single measurement.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -4146,7 +4146,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P5</t>
+          <t>3.7.7-P4</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation by rotational demand and laxity grade rather than by translation.</t>
+          <t>Treat rotational control as the outcome that decides whether a pivoting athlete is satisfied, and as the one the evidence base measures least well.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P6</t>
+          <t>3.7.7-P5</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Repair the lateral posterior horn where it is torn, on rotational grounds.</t>
+          <t>Consider lateral augmentation by rotational demand and laxity grade rather than by translation.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -4196,7 +4196,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.7.7-P7</t>
+          <t>3.7.7-P6</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in a pivoting athlete, particularly before revision.</t>
+          <t>Repair the lateral posterior horn where it is torn, on rotational grounds.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -4221,22 +4221,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P1</t>
+          <t>3.7.7-P7</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.7.8</t>
+          <t>3.7.7</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Applied load and flexion angle, both of which must be stated.</t>
+          <t>Measure slope in a pivoting athlete, particularly before revision.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -4246,7 +4246,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P2</t>
+          <t>3.7.8-P1</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>State load, angle and the instrument's limit of agreement with any figure.</t>
+          <t>Applied load and flexion angle, both of which must be stated.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -4271,7 +4271,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P3</t>
+          <t>3.7.8-P2</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Treat the 3 millimetre threshold as a convention rather than a boundary.</t>
+          <t>State load, angle and the instrument's limit of agreement with any figure.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -4296,7 +4296,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P4</t>
+          <t>3.7.8-P3</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Read the curve shape and the endpoint rather than the number alone.</t>
+          <t>Treat the 3 millimetre threshold as a convention rather than a boundary.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -4321,7 +4321,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P5</t>
+          <t>3.7.8-P4</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Recognise that translation dominates the literature because it is measurable, not because it matters most.</t>
+          <t>Read the curve shape and the endpoint rather than the number alone.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P6</t>
+          <t>3.7.8-P5</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Treat restored anterior translation as a necessary and insufficient result.</t>
+          <t>Recognise that translation dominates the literature because it is measurable, not because it matters most.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -4371,7 +4371,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P7</t>
+          <t>3.7.8-P6</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Treat restored translation as the threshold rather than the goal.</t>
+          <t>Treat restored anterior translation as a necessary and insufficient result.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -4396,7 +4396,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.7.8-P8</t>
+          <t>3.7.8-P7</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Measure serially where progressive laxity is suspected, rather than once.</t>
+          <t>Treat restored translation as the threshold rather than the goal.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -4421,22 +4421,22 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P1</t>
+          <t>3.7.8-P8</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>3.7.9</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Grade under anaesthetic where the grade will change the operation.</t>
+          <t>Measure serially where progressive laxity is suspected, rather than once.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -4446,22 +4446,22 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P2</t>
+          <t>3.7.8-P9</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>3.7.9</t>
+          <t>3.7.8</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Read a high grade as suggesting injury beyond the cruciate alone.</t>
+          <t>Counsel using the weak correlation between laxity and outcome rather than against it.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -4471,7 +4471,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P3</t>
+          <t>3.7.9-P1</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Treat instrumented measures as research tools without a clinical threshold.</t>
+          <t>Grade under anaesthetic where the grade will change the operation.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -4496,7 +4496,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P4</t>
+          <t>3.7.9-P2</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Treat the pivot shift as the clinical sign that corresponds to what the patient reports, and treat its measurement as the weakest link in the whole chapter.</t>
+          <t>Read a high grade as suggesting injury beyond the cruciate alone.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -4521,7 +4521,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P5</t>
+          <t>3.7.9-P3</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Check the pivot shift under anaesthetic after fixation, before leaving theatre.</t>
+          <t>Treat instrumented measures as research tools without a clinical threshold.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -4546,7 +4546,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P6</t>
+          <t>3.7.9-P4</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Add a lateral procedure where a residual shift is anticipated or demonstrated.</t>
+          <t>Treat the pivot shift as the clinical sign that corresponds to what the patient reports, and treat its measurement as the weakest link in the whole chapter.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P7</t>
+          <t>3.7.9-P5</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Address slope and lateral meniscal pathology as part of abolishing the sign.</t>
+          <t>Check the pivot shift under anaesthetic after fixation, before leaving theatre.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -4596,7 +4596,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.7.9-P8</t>
+          <t>3.7.9-P6</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>State the sign's reliability limits when it is used to compare treatments.</t>
+          <t>Add a lateral procedure where a residual shift is anticipated or demonstrated.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -4621,22 +4621,22 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.7.10-P1</t>
+          <t>3.7.9-P7</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>3.7.10</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Stage rehabilitation by flexion angle, since strain is angle dependent.</t>
+          <t>Address slope and lateral meniscal pathology as part of abolishing the sign.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -4646,12 +4646,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.7.10-P2</t>
+          <t>3.7.9-P8</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>3.7.10</t>
+          <t>3.7.9</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Treat the strain data as the mechanical basis of rehabilitation protocols, and treat the protocols as having outrun the data.</t>
+          <t>State the sign's reliability limits when it is used to compare treatments.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -4671,7 +4671,7 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.7.10-P3</t>
+          <t>3.7.10-P1</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Protect the graft in the first months by angle and by loading mode.</t>
+          <t>Stage rehabilitation by flexion angle, since strain is angle dependent.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -4696,7 +4696,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.7.10-P4</t>
+          <t>3.7.10-P2</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Follow outcome based protocols rather than strain based ones where they differ.</t>
+          <t>Treat the strain data as the mechanical basis of rehabilitation protocols, and treat the protocols as having outrun the data.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -4721,7 +4721,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>3.7.10-P5</t>
+          <t>3.7.10-P3</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>State that graft strain in a patient is not measured when discussing protocol choices.</t>
+          <t>Protect the graft in the first months by angle and by loading mode.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
@@ -4746,22 +4746,22 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P1</t>
+          <t>3.7.10-P4</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>3.7.11</t>
+          <t>3.7.10</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Compare activities by peak strain and by direction rather than by force.</t>
+          <t>Follow outcome based protocols rather than strain based ones where they differ.</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr"/>
@@ -4771,22 +4771,22 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P2</t>
+          <t>3.7.10-P5</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>3.7.11</t>
+          <t>3.7.10</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Expect downhill running to load the ligament more than level running.</t>
+          <t>State that graft strain in a patient is not measured when discussing protocol choices.</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P3</t>
+          <t>3.7.11-P1</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Treat fatigue as a loading variable rather than only a performance one.</t>
+          <t>Compare activities by peak strain and by direction rather than by force.</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -4821,7 +4821,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P4</t>
+          <t>3.7.11-P2</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Read running loading estimates as modelled rather than measured.</t>
+          <t>Expect downhill running to load the ligament more than level running.</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
@@ -4846,7 +4846,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P5</t>
+          <t>3.7.11-P3</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Compare activities by peak strain, not peak force.</t>
+          <t>Treat fatigue as a loading variable rather than only a performance one.</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
@@ -4871,7 +4871,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P6</t>
+          <t>3.7.11-P4</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Treat running as the benchmark the other activities are read against, and as the milestone whose safety is mechanically defensible rather than conventional.</t>
+          <t>Read running loading estimates as modelled rather than measured.</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr"/>
@@ -4896,7 +4896,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P7</t>
+          <t>3.7.11-P5</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Stage return to running by criteria rather than by interval.</t>
+          <t>Compare activities by peak strain, not peak force.</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
@@ -4921,7 +4921,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P8</t>
+          <t>3.7.11-P6</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Delay for a concurrent meniscal repair on its own grounds rather than the graft's.</t>
+          <t>Treat running as the benchmark the other activities are read against, and as the milestone whose safety is mechanically defensible rather than conventional.</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
@@ -4946,7 +4946,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P9</t>
+          <t>3.7.11-P7</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Treat gradient and surface as part of the prescription.</t>
+          <t>Stage return to running by criteria rather than by interval.</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>3.7.11-P10</t>
+          <t>3.7.11-P8</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>State that graft load during running is not measured in patients.</t>
+          <t>Delay for a concurrent meniscal repair on its own grounds rather than the graft's.</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr"/>
@@ -4996,22 +4996,22 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P1</t>
+          <t>3.7.11-P9</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>3.7.12</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Address hip and trunk control, which set the position the knee lands in.</t>
+          <t>Treat gradient and surface as part of the prescription.</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr"/>
@@ -5021,22 +5021,22 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P2</t>
+          <t>3.7.11-P10</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>3.7.12</t>
+          <t>3.7.11</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Read landing ligament loading as modelled rather than measured.</t>
+          <t>State that graft load during running is not measured in patients.</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr"/>
@@ -5046,7 +5046,7 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P3</t>
+          <t>3.7.12-P1</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Treat landing mechanics as modifiable risk with modest predictive value for an individual, which is the honest position the prevention literature supports.</t>
+          <t>Address hip and trunk control, which set the position the knee lands in.</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
@@ -5071,7 +5071,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P4</t>
+          <t>3.7.12-P2</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Expect landing asymmetry to persist after reconstruction with normal laxity.</t>
+          <t>Read landing ligament loading as modelled rather than measured.</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr"/>
@@ -5096,7 +5096,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P5</t>
+          <t>3.7.12-P3</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where loading risk seems disproportionate to the injury.</t>
+          <t>Treat landing mechanics as modifiable risk with modest predictive value for an individual, which is the honest position the prevention literature supports.</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>3.7.12-P6</t>
+          <t>3.7.12-P4</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Keep population risk reduction and individual prediction apart when counselling.</t>
+          <t>Expect landing asymmetry to persist after reconstruction with normal laxity.</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr"/>
@@ -5146,22 +5146,22 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P1</t>
+          <t>3.7.12-P5</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>3.7.13</t>
+          <t>3.7.12</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Expect combined loading to reduce the failure load in each direction.</t>
+          <t>Measure slope where loading risk seems disproportionate to the injury.</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
@@ -5171,12 +5171,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P2</t>
+          <t>3.7.12-P6</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>3.7.13</t>
+          <t>3.7.12</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Treat cutting as the activity that defines the reconstruction's job.</t>
+          <t>Keep population risk reduction and individual prediction apart when counselling.</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
@@ -5196,7 +5196,7 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P3</t>
+          <t>3.7.13-P1</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation in a pivoting athlete, on this activity's mechanics.</t>
+          <t>Expect combined loading to reduce the failure load in each direction.</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P4</t>
+          <t>3.7.13-P2</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Measure slope before revising a graft that failed without a new injury.</t>
+          <t>Treat cutting as the activity that defines the reconstruction's job.</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr"/>
@@ -5246,7 +5246,7 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P5</t>
+          <t>3.7.13-P3</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Repair the lateral posterior horn where torn.</t>
+          <t>Consider lateral augmentation in a pivoting athlete, on this activity's mechanics.</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>3.7.13-P6</t>
+          <t>3.7.13-P4</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>State that no assessment reproduces an unanticipated cut when discussing return to sport.</t>
+          <t>Measure slope before revising a graft that failed without a new injury.</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr"/>
@@ -5296,22 +5296,22 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P1</t>
+          <t>3.7.13-P5</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>3.7.14</t>
+          <t>3.7.13</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Expect the associated injuries the mechanism predicts and look for them.</t>
+          <t>Repair the lateral posterior horn where torn.</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr"/>
@@ -5321,22 +5321,22 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P2</t>
+          <t>3.7.13-P6</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>3.7.14</t>
+          <t>3.7.13</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Read bone bruise patterns as evidence about the position at injury.</t>
+          <t>State that no assessment reproduces an unanticipated cut when discussing return to sport.</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr"/>
@@ -5346,7 +5346,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P3</t>
+          <t>3.7.14-P1</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Treat screening as measuring risk factors rather than establishing mechanism.</t>
+          <t>Take the mechanism from the history, since it is usually diagnostic.</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr"/>
@@ -5371,7 +5371,7 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P4</t>
+          <t>3.7.14-P2</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Treat the mechanism as settled in outline and unsettled in detail.</t>
+          <t>Expect the associated injuries the mechanism predicts and look for them.</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr"/>
@@ -5396,7 +5396,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P5</t>
+          <t>3.7.14-P3</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in a young pivoting athlete, particularly before revision.</t>
+          <t>Read bone bruise patterns as evidence about the position at injury.</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
@@ -5421,7 +5421,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P6</t>
+          <t>3.7.14-P4</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Treat previous injury as the strongest risk factor when counselling.</t>
+          <t>Treat screening as measuring risk factors rather than establishing mechanism.</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr"/>
@@ -5446,7 +5446,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>3.7.14-P7</t>
+          <t>3.7.14-P5</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>State that no measurement predicts an individual injury.</t>
+          <t>Treat the mechanism as settled in outline and unsettled in detail.</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
@@ -5471,22 +5471,22 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>3.7.15-P1</t>
+          <t>3.7.14-P6</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>3.7.15</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Treat the hormonal evidence as inconsistent rather than established.</t>
+          <t>Measure slope in a young pivoting athlete, particularly before revision.</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr"/>
@@ -5496,12 +5496,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>3.7.15-P2</t>
+          <t>3.7.14-P7</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>3.7.15</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Treat the rate difference as established and the mechanism as partly explained, and treat that as the basis for prevention rather than for prognosis.</t>
+          <t>Treat previous injury as the strongest risk factor when counselling.</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr"/>
@@ -5521,12 +5521,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>3.7.15-P3</t>
+          <t>3.7.14-P8</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>3.7.15</t>
+          <t>3.7.14</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation in a young female pivoting athlete, on registry reinjury data.</t>
+          <t>State that no measurement predicts an individual injury.</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>3.7.15-P4</t>
+          <t>3.7.15-P1</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Measure slope where a graft failed without a new injury.</t>
+          <t>Treat the hormonal evidence as inconsistent rather than established.</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr"/>
@@ -5571,22 +5571,22 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P1</t>
+          <t>3.7.15-P2</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>3.7.16</t>
+          <t>3.7.15</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Expect fixation to be the limiting factor early and the graft later.</t>
+          <t>Treat the rate difference as established and the mechanism as partly explained, and treat that as the basis for prevention rather than for prognosis.</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
@@ -5596,22 +5596,22 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P2</t>
+          <t>3.7.15-P3</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>3.7.16</t>
+          <t>3.7.15</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Read time zero testing as describing the day of surgery only.</t>
+          <t>Consider lateral augmentation in a young female pivoting athlete, on registry reinjury data.</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr"/>
@@ -5621,12 +5621,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P3</t>
+          <t>3.7.15-P4</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>3.7.16</t>
+          <t>3.7.15</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Treat graft choice as a trade rather than a ranking.</t>
+          <t>Measure slope where a graft failed without a new injury.</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr"/>
@@ -5646,12 +5646,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P4</t>
+          <t>3.7.15-P5</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>3.7.16</t>
+          <t>3.7.15</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Avoid allograft in young active patients, on registry failure data.</t>
+          <t>Counsel on contralateral injury risk as well as graft failure.</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr"/>
@@ -5671,7 +5671,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P5</t>
+          <t>3.7.16-P1</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Read time zero comparisons as a small part of the clinical choice.</t>
+          <t>Expect fixation to be the limiting factor early and the graft later.</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr"/>
@@ -5696,7 +5696,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P6</t>
+          <t>3.7.16-P2</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Plan revision graft choice from tunnel condition and available autograft rather than from the primary algorithm.</t>
+          <t>Read time zero testing as describing the day of surgery only.</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr"/>
@@ -5721,7 +5721,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P7</t>
+          <t>3.7.16-P3</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -5731,12 +5731,12 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Stage with bone grafting where tunnels are wide or confluent.</t>
+          <t>Treat graft choice as a trade rather than a ranking.</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr"/>
@@ -5746,7 +5746,7 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P8</t>
+          <t>3.7.16-P4</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Accept allograft more readily in revision and in multiligament reconstruction.</t>
+          <t>Avoid allograft in young active patients, on registry failure data.</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>3.7.16-P9</t>
+          <t>3.7.16-P5</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>State that fixation choice in compromised bone rests on principle rather than data.</t>
+          <t>Read time zero comparisons as a small part of the clinical choice.</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr"/>
@@ -5796,22 +5796,22 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P1</t>
+          <t>3.7.16-P6</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Place fixation close to the joint line where the technique allows, to reduce graft motion.</t>
+          <t>Plan revision graft choice from tunnel condition and available autograft rather than from the primary algorithm.</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr"/>
@@ -5821,22 +5821,22 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P2</t>
+          <t>3.7.16-P7</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Expect a deep flexion strength deficit after harvest and rehabilitate it.</t>
+          <t>Stage with bone grafting where tunnels are wide or confluent.</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr"/>
@@ -5846,22 +5846,22 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P3</t>
+          <t>3.7.16-P8</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Expect slower healing at the interface than with a bone to bone graft.</t>
+          <t>Accept allograft more readily in revision and in multiligament reconstruction.</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr"/>
@@ -5871,22 +5871,22 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P4</t>
+          <t>3.7.16-P9</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>3.7.17</t>
+          <t>3.7.16</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Treat diameter as the variable that matters most and the one the donor tendon may not allow.</t>
+          <t>State that fixation choice in compromised bone rests on principle rather than data.</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P5</t>
+          <t>3.7.17-P1</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Assess tendon size before surgery rather than discovering it during.</t>
+          <t>Place fixation close to the joint line where the technique allows, to reduce graft motion.</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr"/>
@@ -5921,7 +5921,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P6</t>
+          <t>3.7.17-P2</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Treat a regenerated tendon as unreliable graft material.</t>
+          <t>Expect a deep flexion strength deficit after harvest and rehabilitate it.</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr"/>
@@ -5946,7 +5946,7 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P7</t>
+          <t>3.7.17-P3</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Measure tunnel width before planning a single stage revision.</t>
+          <t>Expect slower healing at the interface than with a bone to bone graft.</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr"/>
@@ -5971,7 +5971,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P8</t>
+          <t>3.7.17-P4</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Consider lateral augmentation to share load where diameter is inadequate.</t>
+          <t>Treat diameter as the variable that matters most and the one the donor tendon may not allow.</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>3.7.17-P9</t>
+          <t>3.7.17-P5</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Plan the graft source before theatre in any revision.</t>
+          <t>Assess tendon size before surgery rather than discovering it during.</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr"/>
@@ -6021,22 +6021,22 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P1</t>
+          <t>3.7.17-P6</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.17</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Expect marginally lower measured laxity and a small effect size.</t>
+          <t>Counsel younger patients on the diameter association with failure.</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr"/>
@@ -6046,22 +6046,22 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P2</t>
+          <t>3.7.17-P7</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.17</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Measure patellar height after harvest where extensor symptoms persist.</t>
+          <t>Treat a regenerated tendon as unreliable graft material.</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr"/>
@@ -6071,22 +6071,22 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P3</t>
+          <t>3.7.17-P8</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.17</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Expect less tunnel widening, which matters if revision is later needed.</t>
+          <t>Measure tunnel width before planning a single stage revision.</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr"/>
@@ -6096,22 +6096,22 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P4</t>
+          <t>3.7.17-P9</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.17</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Treat this graft as the choice where failure rate matters more than donor site, and the hamstring graft as the reverse.</t>
+          <t>Consider lateral augmentation to share load where diameter is inadequate.</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr"/>
@@ -6121,22 +6121,22 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P5</t>
+          <t>3.7.17-P10</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>3.7.18</t>
+          <t>3.7.17</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Consider it where revision is foreseeable, for tunnel preservation.</t>
+          <t>Plan the graft source before theatre in any revision.</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr"/>
@@ -6146,7 +6146,7 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P6</t>
+          <t>3.7.18-P1</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Assess occupation and kneeling demand before choosing.</t>
+          <t>Expect marginally lower measured laxity and a small effect size.</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr"/>
@@ -6171,7 +6171,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>3.7.18-P7</t>
+          <t>3.7.18-P2</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Consider bone plugs where a tunnel defect will not hold a soft tissue graft.</t>
+          <t>Measure patellar height after harvest where extensor symptoms persist.</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr"/>
@@ -6196,12 +6196,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P1</t>
+          <t>3.7.18-P3</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.18</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Expect tendon to bone healing at the soft tissue end.</t>
+          <t>Expect less tunnel widening, which matters if revision is later needed.</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr"/>
@@ -6221,22 +6221,22 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P2</t>
+          <t>3.7.18-P4</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.18</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Read the clinical evidence as shorter and smaller than for the other autografts.</t>
+          <t>Treat this graft as the choice where failure rate matters more than donor site, and the hamstring graft as the reverse.</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr"/>
@@ -6246,12 +6246,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P3</t>
+          <t>3.7.18-P5</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.18</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Treat this graft as the answer to a diameter problem and as the graft whose long term evidence is still accumulating.</t>
+          <t>Consider it where revision is foreseeable, for tunnel preservation.</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr"/>
@@ -6271,12 +6271,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P4</t>
+          <t>3.7.18-P6</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.18</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Use it where diameter cannot be achieved from the hamstrings.</t>
+          <t>Assess occupation and kneeling demand before choosing.</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr"/>
@@ -6296,22 +6296,22 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P5</t>
+          <t>3.7.18-P7</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.18</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>fellowship</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Expect harvest quality to depend on familiarity more than for a simpler harvest.</t>
+          <t>Record patellar height, since it affects later arthroplasty.</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr"/>
@@ -6321,12 +6321,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P6</t>
+          <t>3.7.18-P8</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.18</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Measure tendon thickness on imaging before planning the harvest.</t>
+          <t>Consider bone plugs where a tunnel defect will not hold a soft tissue graft.</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
@@ -6346,12 +6346,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P7</t>
+          <t>3.7.18-P9</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>3.7.19</t>
+          <t>3.7.18</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Consider it first in revision where other donor sites are used.</t>
+          <t>Counsel that a reharvested tendon is feasible and less predictable.</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr"/>
@@ -6371,7 +6371,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>3.7.19-P8</t>
+          <t>3.7.19-P1</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>fellowship</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Expect small numbers in the revision evidence for this graft.</t>
+          <t>Expect tendon to bone healing at the soft tissue end.</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr"/>
@@ -6396,12 +6396,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P1</t>
+          <t>3.7.19-P2</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.19</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Place tunnels anatomically, since position dominates every other variable.</t>
+          <t>Read the clinical evidence as shorter and smaller than for the other autografts.</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr"/>
@@ -6421,22 +6421,22 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P2</t>
+          <t>3.7.19-P3</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.19</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Expect measured laxity to change over the first year without a new injury.</t>
+          <t>Treat this graft as the answer to a diameter problem and as the graft whose long term evidence is still accumulating.</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr"/>
@@ -6446,12 +6446,12 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P3</t>
+          <t>3.7.19-P4</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.19</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Treat the reconstruction as a construct in an environment rather than as an operation.</t>
+          <t>Use it where diameter cannot be achieved from the hamstrings.</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr"/>
@@ -6471,12 +6471,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P4</t>
+          <t>3.7.19-P5</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.19</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in every revision, since it is the commonest unaddressed factor.</t>
+          <t>Counsel that its long term comparative evidence is still accumulating.</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr"/>
@@ -6496,12 +6496,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P5</t>
+          <t>3.7.19-P6</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.19</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Correct the environment as part of the revision rather than afterwards.</t>
+          <t>Expect harvest quality to depend on familiarity more than for a simpler harvest.</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr"/>
@@ -6521,12 +6521,12 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P6</t>
+          <t>3.7.19-P7</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.19</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Plan single or two stage revision from tunnel imaging rather than from preference.</t>
+          <t>Measure tendon thickness on imaging before planning the harvest.</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr"/>
@@ -6546,12 +6546,12 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>3.7.20-P7</t>
+          <t>3.7.19-P8</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>3.7.20</t>
+          <t>3.7.19</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -6561,16 +6561,266 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Correct slope in a knee that has failed a conventional revision.</t>
+          <t>Consider it first in revision where other donor sites are used.</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr"/>
       <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="inlineStr"/>
     </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19-P9</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>3.7.19</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Expect small numbers in the revision evidence for this graft.</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
+      <c r="G145" s="4" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P1</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Place tunnels anatomically, since position dominates every other variable.</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
+      <c r="G146" s="4" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P2</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Expect measured laxity to change over the first year without a new injury.</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
+      <c r="G147" s="4" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P3</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>Treat the reconstruction as a construct in an environment rather than as an operation.</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
+      <c r="G148" s="4" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P4</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Measure slope in every revision, since it is the commonest unaddressed factor.</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
+      <c r="G149" s="4" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P5</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Correct the environment as part of the revision rather than afterwards.</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
+      <c r="G150" s="4" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P6</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Counsel that revision outcomes are worse than primary.</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
+      <c r="G151" s="4" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P7</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>Plan single or two stage revision from tunnel imaging rather than from preference.</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
+      <c r="G152" s="4" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P8</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Correct slope in a knee that has failed a conventional revision.</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
+      <c r="G153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20-P9</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>3.7.20</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>fellowship</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>Share the uncertainty, since no measurement predicts a compromised construct's result.</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
+      <c r="G154" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7257,7 +7507,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>142</f>
+        <f>152</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -7272,7 +7522,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E144,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -7302,7 +7552,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E144,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E154,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -7314,7 +7564,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E144,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E154,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -7326,7 +7576,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E144,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E154,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -7338,7 +7588,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E144,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E154,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
